--- a/Paper/_output/_comparison/crisis_analysis_variable_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_variable_quarterly.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -453,18 +453,22 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="15" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -535,62 +539,82 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>hit_rate_full</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>hit_count_full</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>hit_rate_ptt</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>hit_count_ptt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>hit_rate_ttp</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>hit_count_ttp</t>
         </is>
       </c>
     </row>
@@ -640,34 +664,34 @@
       <c r="M2" t="b">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>2250</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" s="3" t="n">
-        <v>-0.5233370252427383</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="3" t="n">
         <v>-0.5233370252427383</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="R2" s="3" t="n">
+        <v>-0.5233370252427383</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
         <v>888</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" s="3" t="n">
         <v>1.097918346834564</v>
       </c>
-      <c r="W2" s="3" t="inlineStr"/>
       <c r="X2" s="3" t="inlineStr"/>
-      <c r="Y2" s="3" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" s="3" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -715,39 +739,51 @@
       <c r="M3" t="b">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>355</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" s="3" t="n">
-        <v>-0.5346210465276366</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" s="3" t="n">
         <v>-0.5346210465276366</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="R3" s="3" t="n">
+        <v>-0.5346210465276366</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>883</v>
       </c>
-      <c r="T3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" s="3" t="n">
         <v>1.148786472913381</v>
-      </c>
-      <c r="W3" s="3" t="n">
-        <v>0.5</v>
       </c>
       <c r="X3" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Y3" s="3" t="n">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="n">
         <v>0.5</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -796,39 +832,51 @@
       <c r="M4" t="b">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>644</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" s="3" t="n">
-        <v>-0.5406066489371957</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" s="3" t="n">
         <v>-0.5406066489371957</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="R4" s="3" t="n">
+        <v>-0.5406066489371957</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>2417</v>
       </c>
-      <c r="T4" t="n">
-        <v>1529</v>
-      </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" s="3" t="n">
         <v>1.176783790375948</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>0.2</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Y4" s="3" t="n">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="n">
         <v>0.2</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -877,39 +925,51 @@
       <c r="M5" t="b">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" t="n">
         <v>355</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
         <v>-0.4439839127181154</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="R5" s="3" t="n">
+        <v>-0.4439839127181154</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>599</v>
       </c>
-      <c r="T5" t="n">
-        <v>-289</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" s="3" t="n">
         <v>0.798509113087996</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>0.6666666666666666</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="Y5" s="3" t="n">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="n">
         <v>0.6666666666666666</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -958,39 +1018,51 @@
       <c r="M6" t="b">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" t="n">
         <v>355</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" s="3" t="n">
-        <v>-0.5468101317287757</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" s="3" t="n">
         <v>-0.5468101317287757</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R6" s="3" t="n">
+        <v>-0.5468101317287757</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>869</v>
       </c>
-      <c r="T6" t="n">
-        <v>-19</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" s="3" t="n">
         <v>1.206580663011472</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="X6" s="3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="X6" s="3" t="n">
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y6" s="3" t="n">
-        <v>0.5</v>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1039,39 +1111,51 @@
       <c r="M7" t="b">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" t="n">
         <v>355</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" s="3" t="n">
-        <v>-0.5638362806438026</v>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" s="3" t="n">
         <v>-0.5638362806438026</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R7" s="3" t="n">
+        <v>-0.5638362806438026</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
         <v>1006</v>
       </c>
-      <c r="T7" t="n">
-        <v>118</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" s="3" t="n">
         <v>1.292717059264024</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>0.5</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="Y7" s="3" t="n">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="n">
         <v>0.5</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1120,39 +1204,51 @@
       <c r="M8" t="b">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" t="n">
         <v>355</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" s="3" t="n">
-        <v>-0.5315036835710505</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" s="3" t="n">
         <v>-0.5315036835710505</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="R8" s="3" t="n">
+        <v>-0.5315036835710505</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>867</v>
       </c>
-      <c r="T8" t="n">
-        <v>-21</v>
-      </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" s="3" t="n">
         <v>1.134488500619101</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="X8" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y8" s="3" t="n">
-        <v>0.5</v>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1166,7 +1262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1180,17 +1276,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1251,55 +1350,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -1343,35 +1457,44 @@
       <c r="K2" s="3" t="n">
         <v>0.265757517207872</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
+      <c r="L2" s="3" t="n">
+        <v>0.265757517207872</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" s="3" t="n">
+        <v>-0.03939252582908825</v>
+      </c>
+      <c r="Q2" t="n">
         <v>583</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>-55</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="S2" s="3" t="n">
         <v>-0.4859401977791229</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.4862309442441406</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>1313</v>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="b">
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="Y2" s="3" t="n">
         <v>0.9452989626493455</v>
       </c>
     </row>
@@ -1415,35 +1538,42 @@
       <c r="K3" s="3" t="n">
         <v>0.1600179331372341</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.1484663677179584</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>583</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>-55</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="S3" s="3" t="n">
         <v>-0.3701087137927326</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.3856720855668119</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>1049</v>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="b">
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="Y3" s="3" t="n">
         <v>0.5875755418387345</v>
       </c>
     </row>
@@ -1485,35 +1615,44 @@
       <c r="K4" s="3" t="n">
         <v>0.3261125795445277</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
+      <c r="L4" s="3" t="n">
+        <v>0.3261125795445277</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
         <v>1</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" s="3" t="n">
+        <v>-0.06880676405722819</v>
+      </c>
+      <c r="Q4" t="n">
         <v>583</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>-55</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="S4" s="3" t="n">
         <v>-0.5314111816834861</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.5405779751541202</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>1313</v>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="b">
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="Y4" s="3" t="n">
         <v>1.134067141406985</v>
       </c>
     </row>
@@ -1557,35 +1696,42 @@
       <c r="K5" s="3" t="n">
         <v>0.1378626392028849</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.0982768979428859</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>583</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>-55</v>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="S5" s="3" t="n">
         <v>-0.2928258101948606</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.3309499985899496</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>380</v>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="b">
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="Y5" s="3" t="n">
         <v>0.4140787579868381</v>
       </c>
     </row>
@@ -1629,35 +1775,42 @@
       <c r="K6" s="3" t="n">
         <v>0.2108530619377716</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.1956317496068602</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>638</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.4742034398605798</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.4771343763893188</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>994</v>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="b">
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="Y6" s="3" t="n">
         <v>0.9018762689030144</v>
       </c>
     </row>
@@ -1701,35 +1854,42 @@
       <c r="K7" s="3" t="n">
         <v>0.2282498761985527</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.2156281040292364</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>638</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>-0.4893559340541901</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.4938733180213994</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>1054</v>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="b">
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="Y7" s="3" t="n">
         <v>0.9583112126208886</v>
       </c>
     </row>
@@ -1773,35 +1933,42 @@
       <c r="K8" s="3" t="n">
         <v>0.1618137843831609</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.1454631295619674</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>638</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>-0.3962590803105493</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.4021145509405996</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>894</v>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="b">
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="Y8" s="3" t="n">
         <v>0.6563396108953079</v>
       </c>
     </row>
@@ -1816,7 +1983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1830,17 +1997,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1901,55 +2071,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -1995,37 +2180,44 @@
       <c r="K2" s="3" t="n">
         <v>0.2354171526922728</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" s="3" t="n">
+        <v>0.2224417670510091</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>41340</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>355</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="n">
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
         <v>-0.5035092528573126</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.5040024023286764</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>860</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>1.014136226616542</v>
       </c>
     </row>
@@ -2069,37 +2261,44 @@
       <c r="K3" s="3" t="n">
         <v>0.2402269343162137</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.2291230587542065</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>41340</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>355</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>-0.5346210465276369</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.5346210465276369</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>883</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>23</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>1.148786472913382</v>
       </c>
     </row>
@@ -2143,37 +2342,44 @@
       <c r="K4" s="3" t="n">
         <v>0.2132143827670934</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" s="3" t="n">
+        <v>0.1665437946014566</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>41340</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>355</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>-0.4418768397766436</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.4486552572799976</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>475</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>-385</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>0.7917192320057245</v>
       </c>
     </row>
@@ -2217,37 +2423,44 @@
       <c r="K5" s="3" t="n">
         <v>0.1982156637126214</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.1659782200931572</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>41340</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>355</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>-0.4439839127181154</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.4439839127181154</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>599</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>-261</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>0.798509113087996</v>
       </c>
     </row>
@@ -2291,37 +2504,44 @@
       <c r="K6" s="3" t="n">
         <v>0.231793989333857</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.2198273176363286</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>41340</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>355</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.5468101317287759</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.5468101317287759</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>869</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>9</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>1.206580663011473</v>
       </c>
     </row>
@@ -2365,37 +2585,44 @@
       <c r="K7" s="3" t="n">
         <v>0.2483485089561435</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.2483485089561435</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>41340</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>355</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>-0.5638362806438034</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.5638362806438034</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>1006</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>146</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
         <v>1.292717059264028</v>
       </c>
     </row>
@@ -2439,37 +2666,44 @@
       <c r="K8" s="3" t="n">
         <v>0.2301302896387797</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.2180712729983298</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>41340</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>355</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>-0.5315036835710506</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.5315036835710506</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>867</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>7</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>1.134488500619101</v>
       </c>
     </row>
@@ -2484,7 +2718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2498,17 +2732,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2569,55 +2806,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -2663,37 +2915,44 @@
       <c r="K2" s="3" t="n">
         <v>0.08269444253856398</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" s="3" t="n">
+        <v>0.08154585283324596</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>43577</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>64</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="n">
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
         <v>-0.1954368693665691</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.2022979914860074</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>76</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>0.2429105460160748</v>
       </c>
     </row>
@@ -2737,37 +2996,44 @@
       <c r="K3" s="3" t="n">
         <v>0.05878321500570728</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.05436009118223899</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>43577</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>64</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>-0.1647110860703804</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.1648378301232092</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>59</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>-17</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>0.1971905568523549</v>
       </c>
     </row>
@@ -2811,37 +3077,44 @@
       <c r="K4" s="3" t="n">
         <v>0.0794670201188962</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" s="3" t="n">
+        <v>0.0794670201188962</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>43577</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>64</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>-0.1930057479754295</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.1964175293895148</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>80</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>4</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>0.2391661991287057</v>
       </c>
     </row>
@@ -2885,37 +3158,44 @@
       <c r="K5" s="3" t="n">
         <v>0.04694464568316091</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.0428839469005409</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>43577</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>64</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>-0.1379446474939671</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.1410541034597297</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>56</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>-20</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>0.1600183179571426</v>
       </c>
     </row>
@@ -2959,37 +3239,44 @@
       <c r="K6" s="3" t="n">
         <v>0.04865286626178858</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.0406055237404483</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>43577</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>64</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.1377043507659562</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.1461625015373462</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>36</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>-40</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>0.1596950545770186</v>
       </c>
     </row>
@@ -3033,37 +3320,44 @@
       <c r="K7" s="3" t="n">
         <v>0.05204714860336933</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.04168256296557165</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>43577</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>64</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>-0.1406317904810741</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.1492975281333249</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>28</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>-48</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
         <v>0.1636455583571095</v>
       </c>
     </row>
@@ -3107,37 +3401,44 @@
       <c r="K8" s="3" t="n">
         <v>0.05080546557820764</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.04343895480878526</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>43577</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>64</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>-0.1526702520360279</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.1526702520360279</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>41</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>-35</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>0.1801780858076512</v>
       </c>
     </row>
@@ -3152,7 +3453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3166,17 +3467,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3237,55 +3541,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -3331,37 +3650,44 @@
       <c r="K2" s="3" t="n">
         <v>0.1403286526425155</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" s="3" t="n">
+        <v>0.1081518818361314</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>23</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="n">
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
         <v>-0.2902196151348784</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.2902196151348784</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>55</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>0.4088864968986545</v>
       </c>
     </row>
@@ -3405,37 +3731,44 @@
       <c r="K3" s="3" t="n">
         <v>0.1260612834214395</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.1192420364821127</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>23</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>-0.3042808018588748</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.3042808018588748</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>95</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>40</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>0.4373615140589411</v>
       </c>
     </row>
@@ -3479,37 +3812,44 @@
       <c r="K4" s="3" t="n">
         <v>0.1260611393681861</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" s="3" t="n">
+        <v>0.1177292567371861</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>23</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>-0.3050371165491933</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.3050371165491933</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>92</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>37</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>0.4389257668474975</v>
       </c>
     </row>
@@ -3553,37 +3893,44 @@
       <c r="K5" s="3" t="n">
         <v>0.1167974844615735</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.1123208094163259</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>23</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>-0.2902464771828119</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.2902464771828119</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>99</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>44</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>0.4089398190385185</v>
       </c>
     </row>
@@ -3627,37 +3974,44 @@
       <c r="K6" s="3" t="n">
         <v>0.1335580210897492</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.1284389394343405</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>23</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.3203589150179397</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.3203589150179397</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>99</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>44</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>0.47136484549988</v>
       </c>
     </row>
@@ -3701,37 +4055,44 @@
       <c r="K7" s="3" t="n">
         <v>0.1317372817268568</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.1317372817268568</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>23</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>-0.3214421646736139</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.3214421646736139</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>109</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>54</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
         <v>0.4737137321817237</v>
       </c>
     </row>
@@ -3775,37 +4136,44 @@
       <c r="K8" s="3" t="n">
         <v>0.1276281687846577</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.1217344232998122</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>23</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>-0.3068999359996034</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.3068999359996034</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>97</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>42</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>0.4427931145010366</v>
       </c>
     </row>
@@ -3820,7 +4188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3834,17 +4202,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3905,55 +4276,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -3999,37 +4385,44 @@
       <c r="K2" s="3" t="n">
         <v>0.1873955345996986</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" s="3" t="n">
+        <v>0.1811942572807819</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>45300</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>253</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>58</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="S2" s="3" t="n">
         <v>-0.3239608533428744</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.3239608533428744</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>220</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>0.4792042812088533</v>
       </c>
     </row>
@@ -4073,37 +4466,44 @@
       <c r="K3" s="3" t="n">
         <v>0.1696551799768496</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.1474560281169548</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>45300</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>195</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>-0.2929230698083376</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.2929230698083376</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>187</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>-33</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>0.414273266883332</v>
       </c>
     </row>
@@ -4147,37 +4547,44 @@
       <c r="K4" s="3" t="n">
         <v>0.1740571730122129</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" s="3" t="n">
+        <v>0.1740571730122129</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>45300</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>253</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>58</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="S4" s="3" t="n">
         <v>-0.2991318266089934</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.2991318266089934</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>253</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>33</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>0.4268018408678846</v>
       </c>
     </row>
@@ -4221,37 +4628,44 @@
       <c r="K5" s="3" t="n">
         <v>0.1306673287628706</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.1146028285529037</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>45300</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>195</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>-0.2376608476183659</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.2376608476183659</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>194</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>-26</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>0.3117521209239831</v>
       </c>
     </row>
@@ -4295,37 +4709,44 @@
       <c r="K6" s="3" t="n">
         <v>0.2100698038590036</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.17775137249608</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>45300</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>197</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="S6" s="3" t="n">
         <v>-0.3419503932402378</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.3419503932402378</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>165</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>-55</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>0.5196422727520533</v>
       </c>
     </row>
@@ -4369,37 +4790,44 @@
       <c r="K7" s="3" t="n">
         <v>0.215013307989909</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.1824348455939838</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>45300</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>197</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
         <v>2</v>
       </c>
-      <c r="P7" s="3" t="n">
+      <c r="S7" s="3" t="n">
         <v>-0.3454801967968263</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.3454801967968263</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>167</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>-53</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
         <v>0.5278376530489537</v>
       </c>
     </row>
@@ -4443,37 +4871,44 @@
       <c r="K8" s="3" t="n">
         <v>0.2151703805871633</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.1825681188099304</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>45300</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>215</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
         <v>20</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="S8" s="3" t="n">
         <v>-0.3457775114458427</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.3457775114458427</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>149</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>-71</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>0.5285319864347935</v>
       </c>
     </row>
@@ -4488,7 +4923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4502,17 +4937,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4573,55 +5011,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -4667,37 +5120,44 @@
       <c r="K2" s="3" t="n">
         <v>0.1032426212645815</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" s="3" t="n">
+        <v>0.08367967670060625</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>34</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="n">
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
         <v>-0.2242012270138071</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.2242012270138071</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>55</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>0.2889940469367012</v>
       </c>
     </row>
@@ -4741,37 +5201,44 @@
       <c r="K3" s="3" t="n">
         <v>0.08459265268256663</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.06856360039119101</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>34</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>-0.1861905825872663</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.1861905825872663</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>55</v>
       </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>0.2287889260107165</v>
       </c>
     </row>
@@ -4815,37 +5282,44 @@
       <c r="K4" s="3" t="n">
         <v>0.09337303719688129</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" s="3" t="n">
+        <v>0.08328646914822198</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>32</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>-2</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="S4" s="3" t="n">
         <v>-0.1977751279185385</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.1977751279185385</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>76</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>21</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>0.2465332786371843</v>
       </c>
     </row>
@@ -4889,37 +5363,44 @@
       <c r="K5" s="3" t="n">
         <v>0.06348808787815403</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.06348808787815403</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>34</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>-0.1541243129380868</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.1541243129380868</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>102</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>47</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>0.1822068127687015</v>
       </c>
     </row>
@@ -4963,37 +5444,44 @@
       <c r="K6" s="3" t="n">
         <v>0.09021845436612216</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.0808409561365734</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>34</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.1938287231324922</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.1938287231324922</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>75</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>20</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>0.2404311945789499</v>
       </c>
     </row>
@@ -5037,37 +5525,44 @@
       <c r="K7" s="3" t="n">
         <v>0.09605815620571079</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.08489182137059623</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>34</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>-0.2051728224903451</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.2051728224903451</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>72</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>17</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
         <v>0.2581351371667873</v>
       </c>
     </row>
@@ -5111,37 +5606,44 @@
       <c r="K8" s="3" t="n">
         <v>0.08596294066132025</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.08178277122676685</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>34</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>-0.1856244724967976</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.1856244724967976</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>89</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>34</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>0.2279347380021408</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_variable_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_variable_quarterly.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -882,12 +882,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -902,22 +902,22 @@
         <v>39881</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40746</v>
+        <v>40486</v>
       </c>
       <c r="G5" t="n">
-        <v>954</v>
+        <v>775</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="J5" t="n">
-        <v>953</v>
+        <v>774</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1982156637126213</v>
+        <v>0.1532547245176263</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
@@ -931,21 +931,21 @@
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>599</v>
+        <v>420</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="3" t="n">
-        <v>0.798509113087996</v>
+        <v>0.5810273585142876</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -995,22 +995,22 @@
         <v>39881</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>41137</v>
+        <v>40746</v>
       </c>
       <c r="G6" t="n">
-        <v>1224</v>
+        <v>954</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.5468101317287757</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.5468101317287757</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="J6" t="n">
-        <v>1223</v>
+        <v>953</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.2317939893338569</v>
+        <v>0.1982156637126213</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -1024,21 +1024,21 @@
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" s="3" t="n">
-        <v>-0.5468101317287757</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.5468101317287757</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>869</v>
+        <v>599</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="3" t="n">
-        <v>1.206580663011472</v>
+        <v>0.798509113087996</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -1049,31 +1049,31 @@
         </is>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1088,22 +1088,22 @@
         <v>39881</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>41340</v>
+        <v>41137</v>
       </c>
       <c r="G7" t="n">
-        <v>1361</v>
+        <v>1224</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.5638362806438026</v>
+        <v>-0.5468101317287757</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.5638362806438026</v>
+        <v>-0.5468101317287757</v>
       </c>
       <c r="J7" t="n">
-        <v>1360</v>
+        <v>1223</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2483485089561425</v>
+        <v>0.2317939893338569</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -1117,36 +1117,36 @@
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" s="3" t="n">
-        <v>-0.5638362806438026</v>
+        <v>-0.5468101317287757</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-0.5638362806438026</v>
+        <v>-0.5468101317287757</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1006</v>
+        <v>869</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="3" t="n">
-        <v>1.292717059264024</v>
+        <v>1.206580663011472</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AB7" s="3" t="n">
@@ -1161,12 +1161,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1181,22 +1181,22 @@
         <v>39881</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>41135</v>
+        <v>41340</v>
       </c>
       <c r="G8" t="n">
-        <v>1222</v>
+        <v>1361</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.5315036835710505</v>
+        <v>-0.5638362806438026</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.5315036835710505</v>
+        <v>-0.5638362806438026</v>
       </c>
       <c r="J8" t="n">
-        <v>1221</v>
+        <v>1360</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.2301302896387793</v>
+        <v>0.2483485089561425</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -1210,42 +1210,135 @@
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" s="3" t="n">
-        <v>-0.5315036835710505</v>
+        <v>-0.5638362806438026</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>-0.5315036835710505</v>
+        <v>-0.5638362806438026</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>867</v>
+        <v>1006</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="3" t="n">
-        <v>1.134488500619101</v>
+        <v>1.292717059264024</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AB8" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="AC8" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>39881</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>41135</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1222</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>-0.5315036835710505</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>-0.5315036835710505</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1221</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.2301302896387793</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>355</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" s="3" t="n">
+        <v>-0.5315036835710505</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>-0.5315036835710505</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>867</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" s="3" t="n">
+        <v>1.134488500619101</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>3/6</t>
         </is>
@@ -1262,7 +1355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1659,12 +1752,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1679,25 +1772,25 @@
         <v>37460</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>38012</v>
+        <v>37776</v>
       </c>
       <c r="G5" t="n">
-        <v>963</v>
+        <v>801</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2928258101948606</v>
+        <v>-0.2100718359282402</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.3100613758801871</v>
       </c>
       <c r="J5" t="n">
-        <v>813</v>
+        <v>276</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1378626392028849</v>
+        <v>0.1192072642606282</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.0982768979428859</v>
+        <v>0.07750973284135629</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>39364</v>
@@ -1716,34 +1809,34 @@
         <v>-55</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2928258101948606</v>
+        <v>-0.2100718359282402</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.3100613758801871</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>380</v>
+        <v>218</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="b">
         <v>1</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.4140787579868381</v>
+        <v>0.2659378985114353</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1755,28 +1848,28 @@
         <v>36608</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>37538</v>
+        <v>37460</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>38980</v>
+        <v>38012</v>
       </c>
       <c r="G6" t="n">
-        <v>1632</v>
+        <v>963</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.4742034398605798</v>
+        <v>-0.2928258101948606</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.4771343763893188</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="J6" t="n">
-        <v>1628</v>
+        <v>813</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.2108530619377716</v>
+        <v>0.1378626392028849</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1956317496068602</v>
+        <v>0.0982768979428859</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>39364</v>
@@ -1789,40 +1882,40 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>638</v>
+        <v>583</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.4742034398605798</v>
+        <v>-0.2928258101948606</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.4771343763893188</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>994</v>
+        <v>380</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="b">
         <v>1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.9018762689030144</v>
+        <v>0.4140787579868381</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1837,25 +1930,25 @@
         <v>37538</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>39065</v>
+        <v>38980</v>
       </c>
       <c r="G7" t="n">
-        <v>1692</v>
+        <v>1632</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.4893559340541901</v>
+        <v>-0.4742034398605798</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.4938733180213994</v>
+        <v>-0.4771343763893188</v>
       </c>
       <c r="J7" t="n">
-        <v>1687</v>
+        <v>1628</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2282498761985527</v>
+        <v>0.2108530619377716</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2156281040292364</v>
+        <v>0.1956317496068602</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>39364</v>
@@ -1874,34 +1967,34 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.4893559340541901</v>
+        <v>-0.4742034398605798</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.4938733180213994</v>
+        <v>-0.4771343763893188</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1054</v>
+        <v>994</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.9583112126208886</v>
+        <v>0.9018762689030144</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1916,25 +2009,25 @@
         <v>37538</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>38835</v>
+        <v>39065</v>
       </c>
       <c r="G8" t="n">
-        <v>1532</v>
+        <v>1692</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.3962590803105493</v>
+        <v>-0.4893559340541901</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.4021145509405996</v>
+        <v>-0.4938733180213994</v>
       </c>
       <c r="J8" t="n">
-        <v>1524</v>
+        <v>1687</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.1618137843831609</v>
+        <v>0.2282498761985527</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.1454631295619674</v>
+        <v>0.2156281040292364</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>39364</v>
@@ -1953,22 +2046,101 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.3962590803105493</v>
+        <v>-0.4893559340541901</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.4021145509405996</v>
+        <v>-0.4938733180213994</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>894</v>
+        <v>1054</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="b">
         <v>1</v>
       </c>
       <c r="Y8" s="3" t="n">
+        <v>0.9583112126208886</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>36608</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>38835</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1532</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>-0.3962590803105493</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>-0.4021145509405996</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1524</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.1618137843831609</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.1454631295619674</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>638</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.3962590803105493</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-0.4021145509405996</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>894</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>0.6563396108953079</v>
       </c>
     </row>
@@ -1983,7 +2155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2181,10 +2353,10 @@
         <v>0.2354171526922728</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.2224417670510091</v>
+        <v>0.1562892258388244</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>41340</v>
+        <v>43364</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -2262,10 +2434,10 @@
         <v>0.2402269343162137</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2291230587542065</v>
+        <v>0.1609835506580326</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>41340</v>
+        <v>43364</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -2343,10 +2515,10 @@
         <v>0.2132143827670934</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.1665437946014566</v>
+        <v>0.1170148981982912</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>41340</v>
+        <v>43364</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -2386,12 +2558,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2406,28 +2578,28 @@
         <v>39881</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40746</v>
+        <v>40486</v>
       </c>
       <c r="G5" t="n">
-        <v>954</v>
+        <v>775</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="J5" t="n">
-        <v>953</v>
+        <v>774</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1982156637126214</v>
+        <v>0.1532547245176266</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1659782200931572</v>
+        <v>0.08127722777506252</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>41340</v>
+        <v>43364</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -2443,36 +2615,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>599</v>
+        <v>420</v>
       </c>
       <c r="W5" t="n">
-        <v>-261</v>
+        <v>-440</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.798509113087996</v>
+        <v>0.5810273585142876</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2487,28 +2659,28 @@
         <v>39881</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>41137</v>
+        <v>40746</v>
       </c>
       <c r="G6" t="n">
-        <v>1224</v>
+        <v>954</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="J6" t="n">
-        <v>1223</v>
+        <v>953</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.231793989333857</v>
+        <v>0.1982156637126214</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2198273176363286</v>
+        <v>0.1166175213781546</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>41340</v>
+        <v>43364</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -2524,36 +2696,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>869</v>
+        <v>599</v>
       </c>
       <c r="W6" t="n">
-        <v>9</v>
+        <v>-261</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>1.206580663011473</v>
+        <v>0.798509113087996</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2568,28 +2740,28 @@
         <v>39881</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>41340</v>
+        <v>41137</v>
       </c>
       <c r="G7" t="n">
-        <v>1361</v>
+        <v>1224</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="J7" t="n">
-        <v>1360</v>
+        <v>1223</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2483485089561435</v>
+        <v>0.231793989333857</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2483485089561435</v>
+        <v>0.1544522944008473</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>41340</v>
+        <v>43364</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -2605,36 +2777,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1006</v>
+        <v>869</v>
       </c>
       <c r="W7" t="n">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>1.292717059264028</v>
+        <v>1.206580663011473</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2649,28 +2821,28 @@
         <v>39881</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>41135</v>
+        <v>41340</v>
       </c>
       <c r="G8" t="n">
-        <v>1222</v>
+        <v>1361</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.5315036835710506</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.5315036835710506</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="J8" t="n">
-        <v>1221</v>
+        <v>1360</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.2301302896387797</v>
+        <v>0.2483485089561435</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.2180712729983298</v>
+        <v>0.174491493740388</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>41340</v>
+        <v>43364</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -2686,24 +2858,105 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
+        <v>-0.5638362806438034</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-0.5638362806438034</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1006</v>
+      </c>
+      <c r="W8" t="n">
+        <v>146</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>1.292717059264028</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>39881</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>41135</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1222</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>-0.5315036835710506</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>-0.5315036835710506</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="J9" t="n">
+        <v>1221</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.2301302896387797</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.153218484488933</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>43364</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>355</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.5315036835710506</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-0.5315036835710506</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>867</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W9" t="n">
         <v>7</v>
       </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3" t="n">
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>1.134488500619101</v>
       </c>
     </row>
@@ -2718,7 +2971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2916,10 +3169,10 @@
         <v>0.08269444253856398</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.08154585283324596</v>
+        <v>0.05218963375687868</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>43577</v>
+        <v>43880</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -2997,10 +3250,10 @@
         <v>0.05878321500570728</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.05436009118223899</v>
+        <v>0.03479065030557795</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>43577</v>
+        <v>43880</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -3078,10 +3331,10 @@
         <v>0.0794670201188962</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.0794670201188962</v>
+        <v>0.05085917347920408</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>43577</v>
+        <v>43880</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -3121,12 +3374,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3141,28 +3394,28 @@
         <v>43458</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>43542</v>
+        <v>43560</v>
       </c>
       <c r="G5" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.1350492147242662</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.1424709615053656</v>
       </c>
       <c r="J5" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.04694464568316091</v>
+        <v>0.04801488482583489</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.0428839469005409</v>
+        <v>0.02965112288406209</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>43577</v>
+        <v>43880</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -3178,36 +3431,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.1350492147242662</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.1424709615053656</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="W5" t="n">
-        <v>-20</v>
+        <v>-6</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.1600183179571426</v>
+        <v>0.1561351432049565</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3222,28 +3475,28 @@
         <v>43458</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>43511</v>
+        <v>43542</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.1379446474939671</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="J6" t="n">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.04865286626178858</v>
+        <v>0.04694464568316091</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.0406055237404483</v>
+        <v>0.02744587744229462</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>43577</v>
+        <v>43880</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -3259,36 +3512,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.1379446474939671</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="W6" t="n">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.1596950545770186</v>
+        <v>0.1600183179571426</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3303,28 +3556,28 @@
         <v>43458</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>43501</v>
+        <v>43511</v>
       </c>
       <c r="G7" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.1406317904810741</v>
+        <v>-0.1377043507659562</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.1461625015373462</v>
       </c>
       <c r="J7" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.05204714860336933</v>
+        <v>0.04865286626178858</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.04168256296557165</v>
+        <v>0.02598767857457803</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>43577</v>
+        <v>43880</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -3340,36 +3593,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.1406317904810741</v>
+        <v>-0.1377043507659562</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.1461625015373462</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="W7" t="n">
-        <v>-48</v>
+        <v>-40</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.1636455583571095</v>
+        <v>0.1596950545770186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3384,28 +3637,28 @@
         <v>43458</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>43521</v>
+        <v>43501</v>
       </c>
       <c r="G8" t="n">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.1406317904810741</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.1492975281333249</v>
       </c>
       <c r="J8" t="n">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.05080546557820764</v>
+        <v>0.05204714860336933</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.04343895480878526</v>
+        <v>0.02667698748175109</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>43577</v>
+        <v>43880</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -3421,24 +3674,105 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
+        <v>-0.1406317904810741</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-0.1492975281333249</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>28</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-48</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0.1636455583571095</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>43364</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>43521</v>
+      </c>
+      <c r="G9" t="n">
+        <v>105</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>-0.1526702520360279</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>-0.1526702520360279</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="J9" t="n">
+        <v>104</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.05080546557820764</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.02780108446333929</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>64</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.1526702520360279</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-0.1526702520360279</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>41</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W9" t="n">
         <v>-35</v>
       </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3" t="n">
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>0.1801780858076512</v>
       </c>
     </row>
@@ -3453,7 +3787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3651,10 +3985,10 @@
         <v>0.1403286526425155</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1081518818361314</v>
+        <v>0.05728893254440421</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>44069</v>
+        <v>44564</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -3732,10 +4066,10 @@
         <v>0.1260612834214395</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1192420364821127</v>
+        <v>0.06316347777315288</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>44069</v>
+        <v>44564</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -3813,10 +4147,10 @@
         <v>0.1260611393681861</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.1177292567371861</v>
+        <v>0.06236214602293004</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>44069</v>
+        <v>44564</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -3856,12 +4190,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3882,22 +4216,22 @@
         <v>122</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2845422957875736</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2845422957875736</v>
       </c>
       <c r="J5" t="n">
         <v>121</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1167974844615735</v>
+        <v>0.1140968231800305</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1123208094163259</v>
+        <v>0.05812151649835226</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>44069</v>
+        <v>44564</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -3913,10 +4247,10 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2845422957875736</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2845422957875736</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -3931,18 +4265,18 @@
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.3977066626192765</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3963,22 +4297,22 @@
         <v>122</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="J6" t="n">
         <v>121</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1335580210897492</v>
+        <v>0.1167974844615735</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1284389394343405</v>
+        <v>0.05949724743333182</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>44069</v>
+        <v>44564</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -3994,10 +4328,10 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -4012,18 +4346,18 @@
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.47136484549988</v>
+        <v>0.4089398190385185</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4038,28 +4372,28 @@
         <v>43913</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>44069</v>
+        <v>44055</v>
       </c>
       <c r="G7" t="n">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="J7" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1317372817268568</v>
+        <v>0.1335580210897492</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1317372817268568</v>
+        <v>0.06803515216200837</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>44069</v>
+        <v>44564</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -4075,36 +4409,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="W7" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.4737137321817237</v>
+        <v>0.47136484549988</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4119,28 +4453,28 @@
         <v>43913</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>44053</v>
+        <v>44069</v>
       </c>
       <c r="G8" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="J8" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.1276281687846577</v>
+        <v>0.1317372817268568</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.1217344232998122</v>
+        <v>0.06978231093443385</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>44069</v>
+        <v>44564</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -4156,24 +4490,105 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>109</v>
+      </c>
+      <c r="W8" t="n">
+        <v>54</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0.4737137321817237</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>44053</v>
+      </c>
+      <c r="G9" t="n">
+        <v>120</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>-0.3068999359996034</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>-0.3068999359996034</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="J9" t="n">
+        <v>119</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.1276281687846577</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.06448371536726236</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>23</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.3068999359996034</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-0.3068999359996034</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>97</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W9" t="n">
         <v>42</v>
       </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3" t="n">
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>0.4427931145010366</v>
       </c>
     </row>
@@ -4188,7 +4603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4386,10 +4801,10 @@
         <v>0.1873955345996986</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1811942572807819</v>
+        <v>0.1456175032694572</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>45300</v>
+        <v>45707</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -4467,10 +4882,10 @@
         <v>0.1696551799768496</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1474560281169548</v>
+        <v>0.1185036379113724</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>45300</v>
+        <v>45707</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -4548,10 +4963,10 @@
         <v>0.1740571730122129</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.1740571730122129</v>
+        <v>0.1398817564118608</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>45300</v>
+        <v>45707</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -4591,12 +5006,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4608,31 +5023,31 @@
         <v>44564</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>44846</v>
+        <v>44729</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45131</v>
+        <v>45316</v>
       </c>
       <c r="G5" t="n">
-        <v>389</v>
+        <v>517</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="J5" t="n">
-        <v>388</v>
+        <v>516</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1306673287628706</v>
+        <v>0.1197495450449226</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1146028285529037</v>
+        <v>0.09727560120458689</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>45300</v>
+        <v>45707</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -4642,42 +5057,42 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>195</v>
+        <v>115</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>194</v>
+        <v>402</v>
       </c>
       <c r="W5" t="n">
-        <v>-26</v>
+        <v>182</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.3117521209239831</v>
+        <v>0.2849153424233462</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4689,31 +5104,31 @@
         <v>44564</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>44848</v>
+        <v>44846</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45090</v>
+        <v>45131</v>
       </c>
       <c r="G6" t="n">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.3419503932402378</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.3419503932402378</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="J6" t="n">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.2100698038590036</v>
+        <v>0.1306673287628706</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.17775137249608</v>
+        <v>0.09210103019783453</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>45300</v>
+        <v>45707</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -4723,42 +5138,42 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.3419503932402378</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3419503932402378</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="W6" t="n">
-        <v>-55</v>
+        <v>-26</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.5196422727520533</v>
+        <v>0.3117521209239831</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4773,28 +5188,28 @@
         <v>44848</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45092</v>
+        <v>45090</v>
       </c>
       <c r="G7" t="n">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.3454801967968263</v>
+        <v>-0.3419503932402378</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.3454801967968263</v>
+        <v>-0.3419503932402378</v>
       </c>
       <c r="J7" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.215013307989909</v>
+        <v>0.2100698038590036</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1824348455939838</v>
+        <v>0.1428506148817319</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>45300</v>
+        <v>45707</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -4810,36 +5225,36 @@
         <v>2</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3454801967968263</v>
+        <v>-0.3419503932402378</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3454801967968263</v>
+        <v>-0.3419503932402378</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="W7" t="n">
-        <v>-53</v>
+        <v>-55</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.5278376530489537</v>
+        <v>0.5196422727520533</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4851,7 +5266,7 @@
         <v>44564</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>44874</v>
+        <v>44848</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>45092</v>
@@ -4860,22 +5275,22 @@
         <v>364</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.3457775114458427</v>
+        <v>-0.3454801967968263</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.3457775114458427</v>
+        <v>-0.3454801967968263</v>
       </c>
       <c r="J8" t="n">
         <v>363</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.2151703805871633</v>
+        <v>0.215013307989909</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.1825681188099304</v>
+        <v>0.1466145071230273</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>45300</v>
+        <v>45707</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -4885,30 +5300,111 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
+        <v>197</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>-0.3454801967968263</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-0.3454801967968263</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>167</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-53</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0.5278376530489537</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>44874</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>45092</v>
+      </c>
+      <c r="G9" t="n">
+        <v>364</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>-0.3457775114458427</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>-0.3457775114458427</v>
+      </c>
+      <c r="J9" t="n">
+        <v>363</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.2151703805871633</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.14672161268614</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
         <v>215</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>20</v>
       </c>
-      <c r="S8" s="3" t="n">
+      <c r="S9" s="3" t="n">
         <v>-0.3457775114458427</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="T9" s="3" t="n">
         <v>-0.3457775114458427</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>149</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W9" t="n">
         <v>-71</v>
       </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3" t="n">
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>0.5285319864347935</v>
       </c>
     </row>
@@ -4923,7 +5419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5121,10 +5617,10 @@
         <v>0.1032426212645815</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.08367967670060625</v>
+        <v>0.06633642004451831</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>45904</v>
+        <v>46021</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -5202,10 +5698,10 @@
         <v>0.08459265268256663</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.06856360039119101</v>
+        <v>0.05435326682233221</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>45904</v>
+        <v>46021</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -5283,10 +5779,10 @@
         <v>0.09337303719688129</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.08328646914822198</v>
+        <v>0.06602470778189849</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>45904</v>
+        <v>46021</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -5326,12 +5822,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5346,28 +5842,28 @@
         <v>45755</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45904</v>
+        <v>45911</v>
       </c>
       <c r="G5" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="J5" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.06348808787815403</v>
+        <v>0.06042568392595738</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.06348808787815403</v>
+        <v>0.0487682868766525</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>45904</v>
+        <v>46021</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -5383,36 +5879,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="W5" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.1822068127687015</v>
+        <v>0.1422736834243419</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5427,28 +5923,28 @@
         <v>45755</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45866</v>
+        <v>45904</v>
       </c>
       <c r="G6" t="n">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.1541243129380868</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.1541243129380868</v>
       </c>
       <c r="J6" t="n">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.09021845436612216</v>
+        <v>0.06348808787815403</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.0808409561365734</v>
+        <v>0.05032969331821049</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>45904</v>
+        <v>46021</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -5464,36 +5960,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.1541243129380868</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.1541243129380868</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="W6" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.2404311945789499</v>
+        <v>0.1822068127687015</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5508,28 +6004,28 @@
         <v>45755</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45861</v>
+        <v>45866</v>
       </c>
       <c r="G7" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.1938287231324922</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.1938287231324922</v>
       </c>
       <c r="J7" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.09605815620571079</v>
+        <v>0.09021845436612216</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.08489182137059623</v>
+        <v>0.06408604615267784</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>45904</v>
+        <v>46021</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -5545,36 +6041,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.1938287231324922</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.1938287231324922</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="W7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2581351371667873</v>
+        <v>0.2404311945789499</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5589,28 +6085,28 @@
         <v>45755</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45884</v>
+        <v>45861</v>
       </c>
       <c r="G8" t="n">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.1856244724967976</v>
+        <v>-0.2051728224903451</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.1856244724967976</v>
+        <v>-0.2051728224903451</v>
       </c>
       <c r="J8" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.08596294066132025</v>
+        <v>0.09605815620571079</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.08178277122676685</v>
+        <v>0.06729733840789669</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>45904</v>
+        <v>46021</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -5626,24 +6122,105 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
+        <v>-0.2051728224903451</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-0.2051728224903451</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>72</v>
+      </c>
+      <c r="W8" t="n">
+        <v>17</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0.2581351371667873</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="G9" t="n">
+        <v>123</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>-0.1856244724967976</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>-0.1856244724967976</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="J9" t="n">
+        <v>122</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.08596294066132025</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.06483266282103413</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>34</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.1856244724967976</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-0.1856244724967976</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>89</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W9" t="n">
         <v>34</v>
       </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3" t="n">
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>0.2279347380021408</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_variable_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_variable_quarterly.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -882,12 +882,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -902,22 +902,22 @@
         <v>39881</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40486</v>
+        <v>40746</v>
       </c>
       <c r="G5" t="n">
-        <v>775</v>
+        <v>954</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="J5" t="n">
-        <v>774</v>
+        <v>953</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1532547245176263</v>
+        <v>0.1982156637126213</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
@@ -931,21 +931,21 @@
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>420</v>
+        <v>599</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="3" t="n">
-        <v>0.5810273585142876</v>
+        <v>0.798509113087996</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -995,22 +995,22 @@
         <v>39881</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>40746</v>
+        <v>41137</v>
       </c>
       <c r="G6" t="n">
-        <v>954</v>
+        <v>1224</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.5468101317287757</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.5468101317287757</v>
       </c>
       <c r="J6" t="n">
-        <v>953</v>
+        <v>1223</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1982156637126213</v>
+        <v>0.2317939893338569</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -1024,21 +1024,21 @@
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.5468101317287757</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.5468101317287757</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>599</v>
+        <v>869</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="3" t="n">
-        <v>0.798509113087996</v>
+        <v>1.206580663011472</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -1049,31 +1049,31 @@
         </is>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1088,22 +1088,22 @@
         <v>39881</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>41137</v>
+        <v>41340</v>
       </c>
       <c r="G7" t="n">
-        <v>1224</v>
+        <v>1361</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.5468101317287757</v>
+        <v>-0.5638362806438026</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.5468101317287757</v>
+        <v>-0.5638362806438026</v>
       </c>
       <c r="J7" t="n">
-        <v>1223</v>
+        <v>1360</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2317939893338569</v>
+        <v>0.2483485089561425</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -1117,36 +1117,36 @@
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" s="3" t="n">
-        <v>-0.5468101317287757</v>
+        <v>-0.5638362806438026</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-0.5468101317287757</v>
+        <v>-0.5638362806438026</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>869</v>
+        <v>1006</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="3" t="n">
-        <v>1.206580663011472</v>
+        <v>1.292717059264024</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AB7" s="3" t="n">
@@ -1161,12 +1161,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1181,22 +1181,22 @@
         <v>39881</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>41340</v>
+        <v>41135</v>
       </c>
       <c r="G8" t="n">
-        <v>1361</v>
+        <v>1222</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.5638362806438026</v>
+        <v>-0.5315036835710505</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.5638362806438026</v>
+        <v>-0.5315036835710505</v>
       </c>
       <c r="J8" t="n">
-        <v>1360</v>
+        <v>1221</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.2483485089561425</v>
+        <v>0.2301302896387793</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -1210,135 +1210,42 @@
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" s="3" t="n">
-        <v>-0.5638362806438026</v>
+        <v>-0.5315036835710505</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>-0.5638362806438026</v>
+        <v>-0.5315036835710505</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1006</v>
+        <v>867</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="3" t="n">
-        <v>1.292717059264024</v>
+        <v>1.134488500619101</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AB8" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="AC8" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>41135</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1222</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.5315036835710505</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.5315036835710505</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1221</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.2301302896387793</v>
-      </c>
-      <c r="L9" t="b">
-        <v>0</v>
-      </c>
-      <c r="M9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" t="n">
-        <v>355</v>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" s="3" t="n">
-        <v>-0.5315036835710505</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>-0.5315036835710505</v>
-      </c>
-      <c r="S9" t="b">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>867</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" s="3" t="n">
-        <v>1.134488500619101</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC9" t="inlineStr">
         <is>
           <t>3/6</t>
         </is>
@@ -1355,7 +1262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1752,12 +1659,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1772,25 +1679,25 @@
         <v>37460</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>37776</v>
+        <v>38012</v>
       </c>
       <c r="G5" t="n">
-        <v>801</v>
+        <v>963</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2100718359282402</v>
+        <v>-0.2928258101948606</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.3100613758801871</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="J5" t="n">
-        <v>276</v>
+        <v>813</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1192072642606282</v>
+        <v>0.1378626392028849</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.07750973284135629</v>
+        <v>0.0982768979428859</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>39364</v>
@@ -1809,34 +1716,34 @@
         <v>-55</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2100718359282402</v>
+        <v>-0.2928258101948606</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.3100613758801871</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>218</v>
+        <v>380</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="b">
         <v>1</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.2659378985114353</v>
+        <v>0.4140787579868381</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1848,28 +1755,28 @@
         <v>36608</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>37460</v>
+        <v>37538</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>38012</v>
+        <v>38980</v>
       </c>
       <c r="G6" t="n">
-        <v>963</v>
+        <v>1632</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.2928258101948606</v>
+        <v>-0.4742034398605798</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.4771343763893188</v>
       </c>
       <c r="J6" t="n">
-        <v>813</v>
+        <v>1628</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1378626392028849</v>
+        <v>0.2108530619377716</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.0982768979428859</v>
+        <v>0.1956317496068602</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>39364</v>
@@ -1882,40 +1789,40 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>583</v>
+        <v>638</v>
       </c>
       <c r="R6" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.2928258101948606</v>
+        <v>-0.4742034398605798</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.4771343763893188</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>380</v>
+        <v>994</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="b">
         <v>1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.4140787579868381</v>
+        <v>0.9018762689030144</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1930,25 +1837,25 @@
         <v>37538</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>38980</v>
+        <v>39065</v>
       </c>
       <c r="G7" t="n">
-        <v>1632</v>
+        <v>1692</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.4742034398605798</v>
+        <v>-0.4893559340541901</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.4771343763893188</v>
+        <v>-0.4938733180213994</v>
       </c>
       <c r="J7" t="n">
-        <v>1628</v>
+        <v>1687</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2108530619377716</v>
+        <v>0.2282498761985527</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1956317496068602</v>
+        <v>0.2156281040292364</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>39364</v>
@@ -1967,34 +1874,34 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.4742034398605798</v>
+        <v>-0.4893559340541901</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.4771343763893188</v>
+        <v>-0.4938733180213994</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>994</v>
+        <v>1054</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.9018762689030144</v>
+        <v>0.9583112126208886</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2009,25 +1916,25 @@
         <v>37538</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>39065</v>
+        <v>38835</v>
       </c>
       <c r="G8" t="n">
-        <v>1692</v>
+        <v>1532</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.4893559340541901</v>
+        <v>-0.3962590803105493</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.4938733180213994</v>
+        <v>-0.4021145509405996</v>
       </c>
       <c r="J8" t="n">
-        <v>1687</v>
+        <v>1524</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.2282498761985527</v>
+        <v>0.1618137843831609</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.2156281040292364</v>
+        <v>0.1454631295619674</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>39364</v>
@@ -2046,101 +1953,22 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.4893559340541901</v>
+        <v>-0.3962590803105493</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.4938733180213994</v>
+        <v>-0.4021145509405996</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1054</v>
+        <v>894</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="b">
         <v>1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.9583112126208886</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>38835</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1532</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.3962590803105493</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.4021145509405996</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1524</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.1618137843831609</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.1454631295619674</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>638</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.3962590803105493</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.4021145509405996</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>894</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>0.6563396108953079</v>
       </c>
     </row>
@@ -2155,7 +1983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2558,12 +2386,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2578,25 +2406,25 @@
         <v>39881</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40486</v>
+        <v>40746</v>
       </c>
       <c r="G5" t="n">
-        <v>775</v>
+        <v>954</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="J5" t="n">
-        <v>774</v>
+        <v>953</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1532547245176266</v>
+        <v>0.1982156637126214</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.08127722777506252</v>
+        <v>0.1166175213781546</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>43364</v>
@@ -2615,36 +2443,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>420</v>
+        <v>599</v>
       </c>
       <c r="W5" t="n">
-        <v>-440</v>
+        <v>-261</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.5810273585142876</v>
+        <v>0.798509113087996</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2659,25 +2487,25 @@
         <v>39881</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>40746</v>
+        <v>41137</v>
       </c>
       <c r="G6" t="n">
-        <v>954</v>
+        <v>1224</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="J6" t="n">
-        <v>953</v>
+        <v>1223</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1982156637126214</v>
+        <v>0.231793989333857</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1166175213781546</v>
+        <v>0.1544522944008473</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>43364</v>
@@ -2696,36 +2524,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>599</v>
+        <v>869</v>
       </c>
       <c r="W6" t="n">
-        <v>-261</v>
+        <v>9</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.798509113087996</v>
+        <v>1.206580663011473</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2740,25 +2568,25 @@
         <v>39881</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>41137</v>
+        <v>41340</v>
       </c>
       <c r="G7" t="n">
-        <v>1224</v>
+        <v>1361</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="J7" t="n">
-        <v>1223</v>
+        <v>1360</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.231793989333857</v>
+        <v>0.2483485089561435</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1544522944008473</v>
+        <v>0.174491493740388</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>43364</v>
@@ -2777,36 +2605,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>869</v>
+        <v>1006</v>
       </c>
       <c r="W7" t="n">
-        <v>9</v>
+        <v>146</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>1.206580663011473</v>
+        <v>1.292717059264028</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2821,25 +2649,25 @@
         <v>39881</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>41340</v>
+        <v>41135</v>
       </c>
       <c r="G8" t="n">
-        <v>1361</v>
+        <v>1222</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="J8" t="n">
-        <v>1360</v>
+        <v>1221</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.2483485089561435</v>
+        <v>0.2301302896387797</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.174491493740388</v>
+        <v>0.153218484488933</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>43364</v>
@@ -2858,105 +2686,24 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1006</v>
+        <v>867</v>
       </c>
       <c r="W8" t="n">
-        <v>146</v>
+        <v>7</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.292717059264028</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>41135</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1222</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.5315036835710506</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.5315036835710506</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1221</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.2301302896387797</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.153218484488933</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>355</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.5315036835710506</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.5315036835710506</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>867</v>
-      </c>
-      <c r="W9" t="n">
-        <v>7</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>1.134488500619101</v>
       </c>
     </row>
@@ -2971,7 +2718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3374,12 +3121,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3394,25 +3141,25 @@
         <v>43458</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>43560</v>
+        <v>43542</v>
       </c>
       <c r="G5" t="n">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.1350492147242662</v>
+        <v>-0.1379446474939671</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.1424709615053656</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="J5" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.04801488482583489</v>
+        <v>0.04694464568316091</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.02965112288406209</v>
+        <v>0.02744587744229462</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>43880</v>
@@ -3431,36 +3178,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.1350492147242662</v>
+        <v>-0.1379446474939671</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.1424709615053656</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="W5" t="n">
-        <v>-6</v>
+        <v>-20</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.1561351432049565</v>
+        <v>0.1600183179571426</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3475,25 +3222,25 @@
         <v>43458</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>43542</v>
+        <v>43511</v>
       </c>
       <c r="G6" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.1377043507659562</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.1461625015373462</v>
       </c>
       <c r="J6" t="n">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.04694464568316091</v>
+        <v>0.04865286626178858</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.02744587744229462</v>
+        <v>0.02598767857457803</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>43880</v>
@@ -3512,36 +3259,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.1377043507659562</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.1461625015373462</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="W6" t="n">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.1600183179571426</v>
+        <v>0.1596950545770186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3556,25 +3303,25 @@
         <v>43458</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>43511</v>
+        <v>43501</v>
       </c>
       <c r="G7" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.1406317904810741</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.1492975281333249</v>
       </c>
       <c r="J7" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.04865286626178858</v>
+        <v>0.05204714860336933</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.02598767857457803</v>
+        <v>0.02667698748175109</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>43880</v>
@@ -3593,36 +3340,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.1406317904810741</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.1492975281333249</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="W7" t="n">
-        <v>-40</v>
+        <v>-48</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.1596950545770186</v>
+        <v>0.1636455583571095</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3637,25 +3384,25 @@
         <v>43458</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>43501</v>
+        <v>43521</v>
       </c>
       <c r="G8" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.1406317904810741</v>
+        <v>-0.1526702520360279</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.1526702520360279</v>
       </c>
       <c r="J8" t="n">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.05204714860336933</v>
+        <v>0.05080546557820764</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.02667698748175109</v>
+        <v>0.02780108446333929</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>43880</v>
@@ -3674,105 +3421,24 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.1406317904810741</v>
+        <v>-0.1526702520360279</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.1526702520360279</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="W8" t="n">
-        <v>-48</v>
+        <v>-35</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.1636455583571095</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>43521</v>
-      </c>
-      <c r="G9" t="n">
-        <v>105</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.1526702520360279</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.1526702520360279</v>
-      </c>
-      <c r="J9" t="n">
-        <v>104</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.05080546557820764</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.02780108446333929</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>64</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.1526702520360279</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.1526702520360279</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>41</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-35</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>0.1801780858076512</v>
       </c>
     </row>
@@ -3787,7 +3453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4190,12 +3856,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4216,19 +3882,19 @@
         <v>122</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="J5" t="n">
         <v>121</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1140968231800305</v>
+        <v>0.1167974844615735</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.05812151649835226</v>
+        <v>0.05949724743333182</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>44564</v>
@@ -4247,10 +3913,10 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -4265,18 +3931,18 @@
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.3977066626192765</v>
+        <v>0.4089398190385185</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4297,19 +3963,19 @@
         <v>122</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="J6" t="n">
         <v>121</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1167974844615735</v>
+        <v>0.1335580210897492</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.05949724743333182</v>
+        <v>0.06803515216200837</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>44564</v>
@@ -4328,10 +3994,10 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -4346,18 +4012,18 @@
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.47136484549988</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4372,25 +4038,25 @@
         <v>43913</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>44055</v>
+        <v>44069</v>
       </c>
       <c r="G7" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="J7" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1335580210897492</v>
+        <v>0.1317372817268568</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.06803515216200837</v>
+        <v>0.06978231093443385</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>44564</v>
@@ -4409,36 +4075,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="W7" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.47136484549988</v>
+        <v>0.4737137321817237</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4453,25 +4119,25 @@
         <v>43913</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>44069</v>
+        <v>44053</v>
       </c>
       <c r="G8" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="J8" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.1317372817268568</v>
+        <v>0.1276281687846577</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.06978231093443385</v>
+        <v>0.06448371536726236</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>44564</v>
@@ -4490,105 +4156,24 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="W8" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.4737137321817237</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>44053</v>
-      </c>
-      <c r="G9" t="n">
-        <v>120</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="J9" t="n">
-        <v>119</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.1276281687846577</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.06448371536726236</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>23</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>97</v>
-      </c>
-      <c r="W9" t="n">
-        <v>42</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>0.4427931145010366</v>
       </c>
     </row>
@@ -4603,7 +4188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5006,12 +4591,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5023,28 +4608,28 @@
         <v>44564</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>44729</v>
+        <v>44846</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45316</v>
+        <v>45131</v>
       </c>
       <c r="G5" t="n">
-        <v>517</v>
+        <v>389</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="J5" t="n">
-        <v>516</v>
+        <v>388</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1197495450449226</v>
+        <v>0.1306673287628706</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.09727560120458689</v>
+        <v>0.09210103019783453</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>45707</v>
@@ -5057,42 +4642,42 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="R5" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>402</v>
+        <v>194</v>
       </c>
       <c r="W5" t="n">
-        <v>182</v>
+        <v>-26</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.2849153424233462</v>
+        <v>0.3117521209239831</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5104,28 +4689,28 @@
         <v>44564</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>44846</v>
+        <v>44848</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45131</v>
+        <v>45090</v>
       </c>
       <c r="G6" t="n">
-        <v>389</v>
+        <v>362</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3419503932402378</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3419503932402378</v>
       </c>
       <c r="J6" t="n">
-        <v>388</v>
+        <v>361</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1306673287628706</v>
+        <v>0.2100698038590036</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.09210103019783453</v>
+        <v>0.1428506148817319</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>45707</v>
@@ -5138,42 +4723,42 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3419503932402378</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3419503932402378</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="W6" t="n">
-        <v>-26</v>
+        <v>-55</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.3117521209239831</v>
+        <v>0.5196422727520533</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5188,25 +4773,25 @@
         <v>44848</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45090</v>
+        <v>45092</v>
       </c>
       <c r="G7" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.3419503932402378</v>
+        <v>-0.3454801967968263</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.3419503932402378</v>
+        <v>-0.3454801967968263</v>
       </c>
       <c r="J7" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2100698038590036</v>
+        <v>0.215013307989909</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1428506148817319</v>
+        <v>0.1466145071230273</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>45707</v>
@@ -5225,36 +4810,36 @@
         <v>2</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3419503932402378</v>
+        <v>-0.3454801967968263</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3419503932402378</v>
+        <v>-0.3454801967968263</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="W7" t="n">
-        <v>-55</v>
+        <v>-53</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.5196422727520533</v>
+        <v>0.5278376530489537</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5266,7 +4851,7 @@
         <v>44564</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>44848</v>
+        <v>44874</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>45092</v>
@@ -5275,19 +4860,19 @@
         <v>364</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.3454801967968263</v>
+        <v>-0.3457775114458427</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.3454801967968263</v>
+        <v>-0.3457775114458427</v>
       </c>
       <c r="J8" t="n">
         <v>363</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.215013307989909</v>
+        <v>0.2151703805871633</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.1466145071230273</v>
+        <v>0.14672161268614</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>45707</v>
@@ -5300,111 +4885,30 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.3454801967968263</v>
+        <v>-0.3457775114458427</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.3454801967968263</v>
+        <v>-0.3457775114458427</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="W8" t="n">
-        <v>-53</v>
+        <v>-71</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.5278376530489537</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>44874</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>45092</v>
-      </c>
-      <c r="G9" t="n">
-        <v>364</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.3457775114458427</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.3457775114458427</v>
-      </c>
-      <c r="J9" t="n">
-        <v>363</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.2151703805871633</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.14672161268614</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>215</v>
-      </c>
-      <c r="R9" t="n">
-        <v>20</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.3457775114458427</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.3457775114458427</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>149</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-71</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>0.5285319864347935</v>
       </c>
     </row>
@@ -5419,7 +4923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5822,12 +5326,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5842,25 +5346,25 @@
         <v>45755</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45911</v>
+        <v>45904</v>
       </c>
       <c r="G5" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.1541243129380868</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.1541243129380868</v>
       </c>
       <c r="J5" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.06042568392595738</v>
+        <v>0.06348808787815403</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.0487682868766525</v>
+        <v>0.05032969331821049</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>46021</v>
@@ -5879,36 +5383,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.1541243129380868</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.1541243129380868</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="W5" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.1422736834243419</v>
+        <v>0.1822068127687015</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5923,25 +5427,25 @@
         <v>45755</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45904</v>
+        <v>45866</v>
       </c>
       <c r="G6" t="n">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.1938287231324922</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.1938287231324922</v>
       </c>
       <c r="J6" t="n">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.06348808787815403</v>
+        <v>0.09021845436612216</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.05032969331821049</v>
+        <v>0.06408604615267784</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>46021</v>
@@ -5960,36 +5464,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.1938287231324922</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.1938287231324922</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="W6" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.1822068127687015</v>
+        <v>0.2404311945789499</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6004,25 +5508,25 @@
         <v>45755</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45866</v>
+        <v>45861</v>
       </c>
       <c r="G7" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.2051728224903451</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.2051728224903451</v>
       </c>
       <c r="J7" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.09021845436612216</v>
+        <v>0.09605815620571079</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.06408604615267784</v>
+        <v>0.06729733840789669</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>46021</v>
@@ -6041,36 +5545,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.2051728224903451</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.1938287231324922</v>
+        <v>-0.2051728224903451</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="W7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2404311945789499</v>
+        <v>0.2581351371667873</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6085,25 +5589,25 @@
         <v>45755</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45861</v>
+        <v>45884</v>
       </c>
       <c r="G8" t="n">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.1856244724967976</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.1856244724967976</v>
       </c>
       <c r="J8" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.09605815620571079</v>
+        <v>0.08596294066132025</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.06729733840789669</v>
+        <v>0.06483266282103413</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>46021</v>
@@ -6122,105 +5626,24 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.1856244724967976</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.1856244724967976</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="W8" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.2581351371667873</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>45884</v>
-      </c>
-      <c r="G9" t="n">
-        <v>123</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.1856244724967976</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.1856244724967976</v>
-      </c>
-      <c r="J9" t="n">
-        <v>122</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.08596294066132025</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.06483266282103413</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>46021</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>34</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.1856244724967976</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.1856244724967976</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>89</v>
-      </c>
-      <c r="W9" t="n">
-        <v>34</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>0.2279347380021408</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_variable_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_variable_quarterly.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -762,27 +763,27 @@
         <v>1.148786472913381</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -855,27 +856,27 @@
         <v>1.176783790375948</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>2/6</t>
         </is>
       </c>
     </row>
@@ -948,27 +949,27 @@
         <v>0.798509113087996</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -1041,27 +1042,27 @@
         <v>1.206580663011472</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -1134,27 +1135,27 @@
         <v>1.292717059264024</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -1227,27 +1228,27 @@
         <v>1.134488500619101</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -1436,66 +1437,68 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="G2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>-0.4859401977791229</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="J2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.265757517207872</v>
+        <v>0.09032004823014436</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.265757517207872</v>
+        <v>0.04076898034342898</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
       </c>
       <c r="O2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>-0.03939252582908825</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="R2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>-0.4859401977791229</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
       <c r="X2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.9452989626493455</v>
+        <v>0.2044255219913531</v>
       </c>
     </row>
     <row r="3">
@@ -1515,34 +1518,34 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>38980</v>
+        <v>36104</v>
       </c>
       <c r="G3" t="n">
-        <v>1632</v>
+        <v>78</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-0.3701087137927326</v>
+        <v>-0.1695376301830119</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>-0.3856720855668119</v>
+        <v>-0.1710347256874637</v>
       </c>
       <c r="J3" t="n">
-        <v>1606</v>
+        <v>76</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.1600179331372341</v>
+        <v>0.09176628621196273</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1484663677179584</v>
+        <v>0.03947142124256537</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -1552,29 +1555,31 @@
       </c>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="R3" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-0.3701087137927326</v>
+        <v>-0.1695376301830119</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.3856720855668119</v>
+        <v>-0.1710347256874637</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1049</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-8</v>
+      </c>
       <c r="X3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.5875755418387345</v>
+        <v>0.2041484796239155</v>
       </c>
     </row>
     <row r="4">
@@ -1594,66 +1599,68 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
+        <v>36076</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>36119</v>
+      </c>
       <c r="G4" t="n">
-        <v>1896</v>
+        <v>89</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-0.5314111816834861</v>
+        <v>-0.1801769586891863</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0.5405779751541202</v>
+        <v>-0.1840536062106816</v>
       </c>
       <c r="J4" t="n">
-        <v>1889</v>
+        <v>87</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.3261125795445277</v>
+        <v>0.09633253677130151</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.3261125795445277</v>
+        <v>0.0442262701206608</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
       <c r="O4" t="b">
-        <v>1</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>-0.06880676405722819</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>583</v>
+        <v>58</v>
       </c>
       <c r="R4" t="n">
-        <v>-55</v>
+        <v>27</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.5314111816834861</v>
+        <v>-0.1801769586891863</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.5405779751541202</v>
+        <v>-0.1840536062106816</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1313</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-24</v>
+      </c>
       <c r="X4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>1.134067141406985</v>
+        <v>0.2197754266592722</v>
       </c>
     </row>
     <row r="5">
@@ -1673,34 +1680,34 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>38012</v>
+        <v>36104</v>
       </c>
       <c r="G5" t="n">
-        <v>963</v>
+        <v>78</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2928258101948606</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="J5" t="n">
-        <v>813</v>
+        <v>77</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1378626392028849</v>
+        <v>0.08652899115469197</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.0982768979428859</v>
+        <v>0.03721870417281659</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -1710,29 +1717,31 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="R5" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2928258101948606</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>380</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-8</v>
+      </c>
       <c r="X5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.4140787579868381</v>
+        <v>0.1932346188529419</v>
       </c>
     </row>
     <row r="6">
@@ -1752,34 +1761,34 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>38980</v>
+        <v>36104</v>
       </c>
       <c r="G6" t="n">
-        <v>1632</v>
+        <v>78</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.4742034398605798</v>
+        <v>-0.1768263384984526</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.4771343763893188</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="J6" t="n">
-        <v>1628</v>
+        <v>76</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.2108530619377716</v>
+        <v>0.09396824967670085</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1956317496068602</v>
+        <v>0.04041855151300761</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -1789,29 +1798,31 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.4742034398605798</v>
+        <v>-0.1768263384984526</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.4771343763893188</v>
+        <v>-0.1804907434017395</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>994</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-8</v>
+      </c>
       <c r="X6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.9018762689030144</v>
+        <v>0.2148104911130229</v>
       </c>
     </row>
     <row r="7">
@@ -1831,34 +1842,34 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>39065</v>
+        <v>36104</v>
       </c>
       <c r="G7" t="n">
-        <v>1692</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.4893559340541901</v>
+        <v>-0.1757126481189499</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.4938733180213994</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="J7" t="n">
-        <v>1687</v>
+        <v>76</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2282498761985527</v>
+        <v>0.09273364184105239</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2156281040292364</v>
+        <v>0.03988750979864978</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -1868,29 +1879,31 @@
       </c>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.4893559340541901</v>
+        <v>-0.1757126481189499</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.4938733180213994</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1054</v>
-      </c>
-      <c r="W7" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-8</v>
+      </c>
       <c r="X7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.9583112126208886</v>
+        <v>0.213169166939136</v>
       </c>
     </row>
     <row r="8">
@@ -1910,34 +1923,34 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>38835</v>
+        <v>36101</v>
       </c>
       <c r="G8" t="n">
-        <v>1532</v>
+        <v>75</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.3962590803105493</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.4021145509405996</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="J8" t="n">
-        <v>1524</v>
+        <v>73</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.1618137843831609</v>
+        <v>0.085146335583779</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.1454631295619674</v>
+        <v>0.0359218603967827</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -1947,29 +1960,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.3962590803105493</v>
+        <v>-0.164373298400763</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.4021145509405996</v>
+        <v>-0.1696688004536304</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>894</v>
-      </c>
-      <c r="W8" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-11</v>
+      </c>
       <c r="X8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.6563396108953079</v>
+        <v>0.1967066132355302</v>
       </c>
     </row>
   </sheetData>
@@ -2157,68 +2172,66 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>-0.4862309442441406</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>-0.4862309442441406</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.2658275917027504</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.2658275917027504</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>-0.5035092528573126</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>-0.5040024023286764</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.2354171526922728</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.1562892258388244</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="N2" t="b">
         <v>0</v>
       </c>
       <c r="O2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>-0.03993583465459472</v>
+      </c>
       <c r="Q2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>-0.5035092528573126</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>860</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>1.014136226616542</v>
+        <v>0.94639982458421</v>
       </c>
     </row>
     <row r="3">
@@ -2238,34 +2251,34 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>38980</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1631</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>-0.3688137904043242</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>-0.3856720855668119</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1603</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.1600668567184088</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.148505427857176</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>41158</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1238</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>-0.5346210465276369</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>-0.5346210465276369</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1237</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.2402269343162137</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0.1609835506580326</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -2275,31 +2288,29 @@
       </c>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-0.5346210465276369</v>
+        <v>-0.3688137904043242</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.5346210465276369</v>
+        <v>-0.3856720855668119</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>883</v>
-      </c>
-      <c r="W3" t="n">
-        <v>23</v>
-      </c>
+        <v>1049</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>1.148786472913382</v>
+        <v>0.5843185177327912</v>
       </c>
     </row>
     <row r="4">
@@ -2319,68 +2330,66 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1895</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-0.5344887685426145</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>-0.5405779751541202</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1893</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.3261985683606681</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.3261985683606681</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>40568</v>
-      </c>
-      <c r="G4" t="n">
-        <v>830</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>-0.4418768397766436</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>-0.4486552572799976</v>
-      </c>
-      <c r="J4" t="n">
-        <v>815</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0.2132143827670934</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.1170148981982912</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
       <c r="O4" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>-0.07492263356632722</v>
+      </c>
       <c r="Q4" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.4418768397766436</v>
+        <v>-0.5344887685426145</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.4486552572799976</v>
+        <v>-0.5405779751541202</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>475</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-385</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.7917192320057245</v>
+        <v>1.148175881534113</v>
       </c>
     </row>
     <row r="5">
@@ -2400,34 +2409,34 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>38007</v>
+      </c>
+      <c r="G5" t="n">
+        <v>959</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-0.291230325563591</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-0.3309499985899496</v>
+      </c>
+      <c r="J5" t="n">
+        <v>796</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.1381187240689723</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.09828087349740594</v>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>40746</v>
-      </c>
-      <c r="G5" t="n">
-        <v>954</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>-0.4439839127181154</v>
-      </c>
-      <c r="J5" t="n">
-        <v>953</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.1982156637126214</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0.1166175213781546</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -2437,31 +2446,29 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.291230325563591</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>599</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-261</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.798509113087996</v>
+        <v>0.410895578729674</v>
       </c>
     </row>
     <row r="6">
@@ -2481,34 +2488,34 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>38980</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1631</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-0.4746076449481669</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.4771343763893187</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1628</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.2109176516350861</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.1956833334573563</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>41137</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1224</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>-0.5468101317287759</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>-0.5468101317287759</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1223</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.231793989333857</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.1544522944008473</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -2518,31 +2525,29 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.4746076449481669</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.5468101317287759</v>
+        <v>-0.4771343763893187</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>869</v>
-      </c>
-      <c r="W6" t="n">
-        <v>9</v>
-      </c>
+        <v>994</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>1.206580663011473</v>
+        <v>0.9033394574257632</v>
       </c>
     </row>
     <row r="7">
@@ -2562,34 +2567,34 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>39065</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1691</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>-0.4900454549092434</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>-0.4938733180213996</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1688</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.2283173159625294</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.2156849604848136</v>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>41340</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1361</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>-0.5638362806438034</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>-0.5638362806438034</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1360</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0.2483485089561435</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0.174491493740388</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -2599,31 +2604,29 @@
       </c>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.4900454549092434</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.4938733180213996</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1006</v>
-      </c>
-      <c r="W7" t="n">
-        <v>146</v>
-      </c>
+        <v>1054</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>1.292717059264028</v>
+        <v>0.9609590886615789</v>
       </c>
     </row>
     <row r="8">
@@ -2643,34 +2646,34 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>38835</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1531</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>-0.3956369736729513</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>-0.4021145509405994</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1522</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.1618665849188475</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.1455014831147333</v>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>41135</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1222</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>-0.5315036835710506</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>-0.5315036835710506</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1221</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.2301302896387797</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0.153218484488933</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -2680,31 +2683,29 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.5315036835710506</v>
+        <v>-0.3956369736729513</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.5315036835710506</v>
+        <v>-0.4021145509405994</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>867</v>
-      </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
+        <v>894</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.134488500619101</v>
+        <v>0.6546346424886254</v>
       </c>
     </row>
   </sheetData>
@@ -2892,34 +2893,34 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="G2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="J2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.08269444253856398</v>
+        <v>0.2354171526922728</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.05218963375687868</v>
+        <v>0.1563175570682493</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -2929,22 +2930,22 @@
       </c>
       <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -2953,7 +2954,7 @@
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.2429105460160748</v>
+        <v>1.014136226616542</v>
       </c>
     </row>
     <row r="3">
@@ -2973,34 +2974,34 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>43545</v>
+        <v>41158</v>
       </c>
       <c r="G3" t="n">
-        <v>123</v>
+        <v>1238</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-0.1647110860703804</v>
+        <v>-0.5346210465276369</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>-0.1648378301232092</v>
+        <v>-0.5346210465276369</v>
       </c>
       <c r="J3" t="n">
-        <v>121</v>
+        <v>1237</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.05878321500570728</v>
+        <v>0.2402269343162137</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.03479065030557795</v>
+        <v>0.1610127328481859</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -3010,31 +3011,31 @@
       </c>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-0.1647110860703804</v>
+        <v>-0.5346210465276369</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.1648378301232092</v>
+        <v>-0.5346210465276369</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>59</v>
+        <v>883</v>
       </c>
       <c r="W3" t="n">
-        <v>-17</v>
+        <v>23</v>
       </c>
       <c r="X3" t="b">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.1971905568523549</v>
+        <v>1.148786472913382</v>
       </c>
     </row>
     <row r="4">
@@ -3054,34 +3055,34 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>43577</v>
+        <v>40568</v>
       </c>
       <c r="G4" t="n">
-        <v>144</v>
+        <v>830</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.4418768397766436</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.4486552572799976</v>
       </c>
       <c r="J4" t="n">
-        <v>138</v>
+        <v>815</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.0794670201188962</v>
+        <v>0.2132143827670934</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.05085917347920408</v>
+        <v>0.1170361099990996</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -3091,31 +3092,31 @@
       </c>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.4418768397766436</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.4486552572799976</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>80</v>
+        <v>475</v>
       </c>
       <c r="W4" t="n">
-        <v>4</v>
+        <v>-385</v>
       </c>
       <c r="X4" t="b">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.2391661991287057</v>
+        <v>0.7917192320057245</v>
       </c>
     </row>
     <row r="5">
@@ -3135,34 +3136,34 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>43542</v>
+        <v>40746</v>
       </c>
       <c r="G5" t="n">
-        <v>120</v>
+        <v>954</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="J5" t="n">
-        <v>116</v>
+        <v>953</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.04694464568316091</v>
+        <v>0.1982156637126214</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.02744587744229462</v>
+        <v>0.1166386611447342</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -3172,31 +3173,31 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>56</v>
+        <v>599</v>
       </c>
       <c r="W5" t="n">
-        <v>-20</v>
+        <v>-261</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.1600183179571426</v>
+        <v>0.798509113087996</v>
       </c>
     </row>
     <row r="6">
@@ -3216,34 +3217,34 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>43511</v>
+        <v>41137</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>1224</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="J6" t="n">
-        <v>90</v>
+        <v>1223</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.04865286626178858</v>
+        <v>0.231793989333857</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.02598767857457803</v>
+        <v>0.154480292641701</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -3253,31 +3254,31 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.1377043507659562</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.1461625015373462</v>
+        <v>-0.5468101317287759</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>36</v>
+        <v>869</v>
       </c>
       <c r="W6" t="n">
-        <v>-40</v>
+        <v>9</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.1596950545770186</v>
+        <v>1.206580663011473</v>
       </c>
     </row>
     <row r="7">
@@ -3297,34 +3298,34 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>43501</v>
+        <v>41340</v>
       </c>
       <c r="G7" t="n">
-        <v>92</v>
+        <v>1361</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.1406317904810741</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="J7" t="n">
-        <v>81</v>
+        <v>1360</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.05204714860336933</v>
+        <v>0.2483485089561435</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.02667698748175109</v>
+        <v>0.1745231245742816</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -3334,31 +3335,31 @@
       </c>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.1406317904810741</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>28</v>
+        <v>1006</v>
       </c>
       <c r="W7" t="n">
-        <v>-48</v>
+        <v>146</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.1636455583571095</v>
+        <v>1.292717059264028</v>
       </c>
     </row>
     <row r="8">
@@ -3378,34 +3379,34 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>43521</v>
+        <v>41135</v>
       </c>
       <c r="G8" t="n">
-        <v>105</v>
+        <v>1222</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="J8" t="n">
-        <v>104</v>
+        <v>1221</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.05080546557820764</v>
+        <v>0.2301302896387797</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.02780108446333929</v>
+        <v>0.1532462590716843</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -3415,31 +3416,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.1526702520360279</v>
+        <v>-0.5315036835710506</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>41</v>
+        <v>867</v>
       </c>
       <c r="W8" t="n">
-        <v>-35</v>
+        <v>7</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.1801780858076512</v>
+        <v>1.134488500619101</v>
       </c>
     </row>
   </sheetData>
@@ -3627,34 +3628,34 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="G2" t="n">
+        <v>143</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>-0.1989728318606708</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>-0.2022979914860072</v>
+      </c>
+      <c r="J2" t="n">
+        <v>138</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.08183226369428324</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.05211846719049073</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="G2" t="n">
-        <v>78</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="J2" t="n">
-        <v>77</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.1403286526425155</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.05728893254440421</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -3664,22 +3665,22 @@
       </c>
       <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606708</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -3688,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.4088864968986545</v>
+        <v>0.2483971078320053</v>
       </c>
     </row>
     <row r="3">
@@ -3708,34 +3709,34 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>43545</v>
+      </c>
+      <c r="G3" t="n">
+        <v>124</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>-0.1658685120345931</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>-0.1658685120345931</v>
+      </c>
+      <c r="J3" t="n">
+        <v>123</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.05949664240311516</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.03530476196406786</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>44049</v>
-      </c>
-      <c r="G3" t="n">
-        <v>118</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>-0.3042808018588748</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>-0.3042808018588748</v>
-      </c>
-      <c r="J3" t="n">
-        <v>117</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.1260612834214395</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0.06316347777315288</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -3745,31 +3746,31 @@
       </c>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-0.3042808018588748</v>
+        <v>-0.1658685120345931</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.3042808018588748</v>
+        <v>-0.1658685120345931</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="W3" t="n">
-        <v>40</v>
+        <v>-19</v>
       </c>
       <c r="X3" t="b">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.4373615140589411</v>
+        <v>0.198851757100281</v>
       </c>
     </row>
     <row r="4">
@@ -3789,34 +3790,34 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="G4" t="n">
+        <v>146</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-0.1950653726524902</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>-0.1964175293895147</v>
+      </c>
+      <c r="J4" t="n">
+        <v>143</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.07892753856493077</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.05078939621381112</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>44046</v>
-      </c>
-      <c r="G4" t="n">
-        <v>115</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="J4" t="n">
-        <v>114</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0.1260611393681861</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.06236214602293004</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -3826,31 +3827,31 @@
       </c>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1950653726524902</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1964175293895147</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="W4" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="X4" t="b">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.4389257668474975</v>
+        <v>0.2423369128686717</v>
       </c>
     </row>
     <row r="5">
@@ -3870,34 +3871,34 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>43539</v>
+      </c>
+      <c r="G5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-0.1373591481699221</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-0.1410541034597296</v>
+      </c>
+      <c r="J5" t="n">
+        <v>115</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.04694462358448135</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.0274071811141844</v>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="G5" t="n">
-        <v>122</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="J5" t="n">
-        <v>121</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.1167974844615735</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0.05949724743333182</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -3907,31 +3908,31 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1373591481699221</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="W5" t="n">
-        <v>44</v>
+        <v>-23</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1592309799362237</v>
       </c>
     </row>
     <row r="6">
@@ -3951,34 +3952,34 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>43511</v>
+      </c>
+      <c r="G6" t="n">
+        <v>101</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-0.1393233790300028</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.1461625015373463</v>
+      </c>
+      <c r="J6" t="n">
+        <v>93</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.04842348838498468</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.02595625199141308</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="G6" t="n">
-        <v>122</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>-0.3203589150179397</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>-0.3203589150179397</v>
-      </c>
-      <c r="J6" t="n">
-        <v>121</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.1335580210897492</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.06803515216200837</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -3988,31 +3989,31 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1393233790300028</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3203589150179397</v>
+        <v>-0.1461625015373463</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="W6" t="n">
-        <v>44</v>
+        <v>-42</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.47136484549988</v>
+        <v>0.1618765697074274</v>
       </c>
     </row>
     <row r="7">
@@ -4032,34 +4033,34 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>43515</v>
+      </c>
+      <c r="G7" t="n">
+        <v>102</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>-0.1428942080320033</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>-0.1492975281333248</v>
+      </c>
+      <c r="J7" t="n">
+        <v>93</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.04978003260477074</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.02681387698071469</v>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>44069</v>
-      </c>
-      <c r="G7" t="n">
-        <v>132</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>-0.3214421646736139</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>-0.3214421646736139</v>
-      </c>
-      <c r="J7" t="n">
-        <v>131</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0.1317372817268568</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0.06978231093443385</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -4069,31 +4070,31 @@
       </c>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1428942080320033</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="W7" t="n">
-        <v>54</v>
+        <v>-41</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.4737137321817237</v>
+        <v>0.1667171186696854</v>
       </c>
     </row>
     <row r="8">
@@ -4113,34 +4114,34 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>43521</v>
+      </c>
+      <c r="G8" t="n">
+        <v>106</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>-0.154217499687799</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>-0.154217499687799</v>
+      </c>
+      <c r="J8" t="n">
+        <v>105</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.05190748421809096</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.02849756106243677</v>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>44053</v>
-      </c>
-      <c r="G8" t="n">
-        <v>120</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>-0.3068999359996034</v>
-      </c>
-      <c r="J8" t="n">
-        <v>119</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.1276281687846577</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0.06448371536726236</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -4150,31 +4151,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.3068999359996034</v>
+        <v>-0.154217499687799</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="W8" t="n">
-        <v>42</v>
+        <v>-37</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.4427931145010366</v>
+        <v>0.1823370661261887</v>
       </c>
     </row>
   </sheetData>
@@ -4362,34 +4363,34 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="G2" t="n">
+        <v>78</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="J2" t="n">
+        <v>77</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.1403286526425155</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.05728893254440421</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="G2" t="n">
-        <v>473</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>-0.3239608533428744</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>-0.3239608533428744</v>
-      </c>
-      <c r="J2" t="n">
-        <v>472</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.1873955345996986</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.1456175032694572</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -4399,22 +4400,22 @@
       </c>
       <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="R2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -4423,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.4792042812088533</v>
+        <v>0.4088864968986545</v>
       </c>
     </row>
     <row r="3">
@@ -4443,34 +4444,34 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>44049</v>
+      </c>
+      <c r="G3" t="n">
+        <v>118</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>-0.3042808018588748</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>-0.3042808018588748</v>
+      </c>
+      <c r="J3" t="n">
+        <v>117</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.1260612834214395</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.06316347777315288</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>45120</v>
-      </c>
-      <c r="G3" t="n">
-        <v>382</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>-0.2929230698083376</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>-0.2929230698083376</v>
-      </c>
-      <c r="J3" t="n">
-        <v>381</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.1696551799768496</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0.1185036379113724</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -4480,31 +4481,31 @@
       </c>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-0.2929230698083376</v>
+        <v>-0.3042808018588748</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.2929230698083376</v>
+        <v>-0.3042808018588748</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>187</v>
+        <v>95</v>
       </c>
       <c r="W3" t="n">
-        <v>-33</v>
+        <v>40</v>
       </c>
       <c r="X3" t="b">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.414273266883332</v>
+        <v>0.4373615140589411</v>
       </c>
     </row>
     <row r="4">
@@ -4524,34 +4525,34 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>44046</v>
+      </c>
+      <c r="G4" t="n">
+        <v>115</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-0.3050371165491933</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>-0.3050371165491933</v>
+      </c>
+      <c r="J4" t="n">
+        <v>114</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.1260611393681861</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.06236214602293004</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>45300</v>
-      </c>
-      <c r="G4" t="n">
-        <v>506</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>-0.2991318266089934</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>-0.2991318266089934</v>
-      </c>
-      <c r="J4" t="n">
-        <v>505</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0.1740571730122129</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.1398817564118608</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -4561,31 +4562,31 @@
       </c>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="R4" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.2991318266089934</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.2991318266089934</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>253</v>
+        <v>92</v>
       </c>
       <c r="W4" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="X4" t="b">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.4268018408678846</v>
+        <v>0.4389257668474975</v>
       </c>
     </row>
     <row r="5">
@@ -4605,34 +4606,34 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="G5" t="n">
+        <v>122</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="J5" t="n">
+        <v>121</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.1167974844615735</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.05949724743333182</v>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>45131</v>
-      </c>
-      <c r="G5" t="n">
-        <v>389</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>-0.2376608476183659</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>-0.2376608476183659</v>
-      </c>
-      <c r="J5" t="n">
-        <v>388</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.1306673287628706</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0.09210103019783453</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -4642,31 +4643,31 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="W5" t="n">
-        <v>-26</v>
+        <v>44</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.3117521209239831</v>
+        <v>0.4089398190385185</v>
       </c>
     </row>
     <row r="6">
@@ -4686,34 +4687,34 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="G6" t="n">
+        <v>122</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-0.3203589150179397</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.3203589150179397</v>
+      </c>
+      <c r="J6" t="n">
+        <v>121</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.1335580210897492</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.06803515216200837</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>45090</v>
-      </c>
-      <c r="G6" t="n">
-        <v>362</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>-0.3419503932402378</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>-0.3419503932402378</v>
-      </c>
-      <c r="J6" t="n">
-        <v>361</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.2100698038590036</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.1428506148817319</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -4723,31 +4724,31 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.3419503932402378</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3419503932402378</v>
+        <v>-0.3203589150179397</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>165</v>
+        <v>99</v>
       </c>
       <c r="W6" t="n">
-        <v>-55</v>
+        <v>44</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.5196422727520533</v>
+        <v>0.47136484549988</v>
       </c>
     </row>
     <row r="7">
@@ -4767,34 +4768,34 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="G7" t="n">
+        <v>132</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>-0.3214421646736139</v>
+      </c>
+      <c r="J7" t="n">
+        <v>131</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.1317372817268568</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.06978231093443385</v>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>45092</v>
-      </c>
-      <c r="G7" t="n">
-        <v>364</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>-0.3454801967968263</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>-0.3454801967968263</v>
-      </c>
-      <c r="J7" t="n">
-        <v>363</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0.215013307989909</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0.1466145071230273</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -4804,31 +4805,31 @@
       </c>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3454801967968263</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3454801967968263</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>167</v>
+        <v>109</v>
       </c>
       <c r="W7" t="n">
-        <v>-53</v>
+        <v>54</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.5278376530489537</v>
+        <v>0.4737137321817237</v>
       </c>
     </row>
     <row r="8">
@@ -4848,34 +4849,34 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>44053</v>
+      </c>
+      <c r="G8" t="n">
+        <v>120</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>-0.3068999359996034</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>-0.3068999359996034</v>
+      </c>
+      <c r="J8" t="n">
+        <v>119</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.1276281687846577</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.06448371536726236</v>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>44874</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>45092</v>
-      </c>
-      <c r="G8" t="n">
-        <v>364</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>-0.3457775114458427</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>-0.3457775114458427</v>
-      </c>
-      <c r="J8" t="n">
-        <v>363</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.2151703805871633</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0.14672161268614</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -4885,31 +4886,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="R8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.3457775114458427</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.3457775114458427</v>
+        <v>-0.3068999359996034</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>149</v>
+        <v>97</v>
       </c>
       <c r="W8" t="n">
-        <v>-71</v>
+        <v>42</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.5285319864347935</v>
+        <v>0.4427931145010366</v>
       </c>
     </row>
   </sheetData>
@@ -5097,6 +5098,741 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="G2" t="n">
+        <v>473</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>-0.3239608533428744</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>-0.3239608533428744</v>
+      </c>
+      <c r="J2" t="n">
+        <v>472</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.1873955345996986</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.1456175032694572</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>253</v>
+      </c>
+      <c r="R2" t="n">
+        <v>58</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>-0.3239608533428744</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>-0.3239608533428744</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>220</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>0.4792042812088533</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>equal_weight</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>equal_t_10</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>45120</v>
+      </c>
+      <c r="G3" t="n">
+        <v>382</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>-0.2929230698083376</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>-0.2929230698083376</v>
+      </c>
+      <c r="J3" t="n">
+        <v>381</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.1696551799768496</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.1185036379113724</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>-0.2929230698083376</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>-0.2929230698083376</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>187</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-33</v>
+      </c>
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>0.414273266883332</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>45300</v>
+      </c>
+      <c r="G4" t="n">
+        <v>506</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-0.2991318266089934</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>-0.2991318266089934</v>
+      </c>
+      <c r="J4" t="n">
+        <v>505</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.1740571730122129</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.1398817564118608</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>253</v>
+      </c>
+      <c r="R4" t="n">
+        <v>58</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>-0.2991318266089934</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-0.2991318266089934</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>253</v>
+      </c>
+      <c r="W4" t="n">
+        <v>33</v>
+      </c>
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>0.4268018408678846</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>45131</v>
+      </c>
+      <c r="G5" t="n">
+        <v>389</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="J5" t="n">
+        <v>388</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.1306673287628706</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.09210103019783453</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>195</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>-0.2376608476183659</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>194</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-26</v>
+      </c>
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0.3117521209239831</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>45090</v>
+      </c>
+      <c r="G6" t="n">
+        <v>362</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-0.3419503932402378</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.3419503932402378</v>
+      </c>
+      <c r="J6" t="n">
+        <v>361</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.2100698038590036</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.1428506148817319</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>197</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>-0.3419503932402378</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-0.3419503932402378</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>165</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-55</v>
+      </c>
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0.5196422727520533</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>45092</v>
+      </c>
+      <c r="G7" t="n">
+        <v>364</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>-0.3454801967968263</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>-0.3454801967968263</v>
+      </c>
+      <c r="J7" t="n">
+        <v>363</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.215013307989909</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.1466145071230273</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>197</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>-0.3454801967968263</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>-0.3454801967968263</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>167</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-53</v>
+      </c>
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0.5278376530489537</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>44874</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>45092</v>
+      </c>
+      <c r="G8" t="n">
+        <v>364</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>-0.3457775114458427</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>-0.3457775114458427</v>
+      </c>
+      <c r="J8" t="n">
+        <v>363</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.2151703805871633</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.14672161268614</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>215</v>
+      </c>
+      <c r="R8" t="n">
+        <v>20</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>-0.3457775114458427</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-0.3457775114458427</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>149</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-71</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0.5285319864347935</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="E2" s="2" t="n">
